--- a/Grade&Con_Compara.xlsx
+++ b/Grade&Con_Compara.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E266"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10003035</t>
+          <t>10001619</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -469,17 +469,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10003524</t>
+          <t>10001806</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -492,12 +492,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10005879</t>
+          <t>10002252</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10008147</t>
+          <t>10007229</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -538,17 +538,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10010161</t>
+          <t>10007754</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -561,7 +561,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10010949</t>
+          <t>10009188</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10011579</t>
+          <t>10009651</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10012222</t>
+          <t>10011043</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>X-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10014159</t>
+          <t>10011461</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -653,12 +653,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10016451</t>
+          <t>10013059</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -676,17 +676,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10016823</t>
+          <t>10013349</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -699,7 +699,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10016998</t>
+          <t>10013764</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -722,17 +722,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10018831</t>
+          <t>10013956</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -745,17 +745,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100485</t>
+          <t>10015023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -768,7 +768,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>101704</t>
+          <t>10016760</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -791,17 +791,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>101803</t>
+          <t>10017752</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -814,17 +814,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>101806</t>
+          <t>10018833</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -837,7 +837,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>101922</t>
+          <t>1003192</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -860,12 +860,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>102236</t>
+          <t>101074</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -883,17 +883,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>102297</t>
+          <t>101646</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -906,12 +906,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>102653</t>
+          <t>103977</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -929,17 +929,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>105206</t>
+          <t>104245</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -952,17 +952,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>105221</t>
+          <t>104823</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -975,17 +975,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>105691</t>
+          <t>105036</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -998,17 +998,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>106148</t>
+          <t>106151</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1021,7 +1021,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>106199</t>
+          <t>108072</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1044,17 +1044,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>106325</t>
+          <t>108308</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1067,7 +1067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>106408</t>
+          <t>108312</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1090,17 +1090,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>107003</t>
+          <t>108361</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1113,7 +1113,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>108607</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1136,17 +1136,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>108375</t>
+          <t>108625</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1159,17 +1159,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>110213</t>
+          <t>109073</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1182,17 +1182,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1102413</t>
+          <t>110240</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1205,12 +1205,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>113319</t>
+          <t>110976</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1309436</t>
+          <t>111861</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1251,7 +1251,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>112362</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1274,17 +1274,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1315088</t>
+          <t>113408</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1297,12 +1297,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1400342</t>
+          <t>114030</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1401039</t>
+          <t>1303173</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1343,12 +1343,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1603328</t>
+          <t>1303833</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1603468</t>
+          <t>1305866</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1389,17 +1389,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1603989</t>
+          <t>1307898</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1412,7 +1412,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1604271</t>
+          <t>1308834</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1435,17 +1435,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1604273</t>
+          <t>1400131</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1458,7 +1458,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1604316</t>
+          <t>1400928</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1605104</t>
+          <t>1401086</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1605469</t>
+          <t>1401197</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1605572</t>
+          <t>1601450</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1605664</t>
+          <t>1602160</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1573,17 +1573,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1606254</t>
+          <t>1602494</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1596,12 +1596,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1608539</t>
+          <t>1603162</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1608896</t>
+          <t>1604572</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1642,17 +1642,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1609072</t>
+          <t>1604620</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1665,7 +1665,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1609301</t>
+          <t>1605583</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1688,7 +1688,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1610007</t>
+          <t>1605744</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1610509</t>
+          <t>1605803</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1610855</t>
+          <t>1607131</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1757,17 +1757,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1612436</t>
+          <t>1608523</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1780,12 +1780,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1613202</t>
+          <t>1608554</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1803,17 +1803,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1613624</t>
+          <t>1609216</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1826,17 +1826,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1615287</t>
+          <t>1615341</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1849,12 +1849,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1615315</t>
+          <t>1616828</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1872,17 +1872,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1615346</t>
+          <t>1617868</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1895,12 +1895,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1617442</t>
+          <t>1618142</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1619039</t>
+          <t>1618327</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1619480</t>
+          <t>1619026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1964,12 +1964,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1620620</t>
+          <t>1619154</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1621608</t>
+          <t>1619509</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1626845</t>
+          <t>1620561</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2033,7 +2033,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1627258</t>
+          <t>1620621</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2056,17 +2056,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1627631</t>
+          <t>1623442</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2079,7 +2079,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1627951</t>
+          <t>1626785</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2102,17 +2102,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1900892</t>
+          <t>1627634</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2125,17 +2125,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1902157</t>
+          <t>1627856</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2148,17 +2148,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1902251</t>
+          <t>1628389</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2171,17 +2171,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1902448</t>
+          <t>1700254</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2194,7 +2194,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2000762</t>
+          <t>1702457</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2217,17 +2217,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2000764</t>
+          <t>1901168</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2240,17 +2240,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2003192</t>
+          <t>1901987</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2263,12 +2263,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2014158</t>
+          <t>1902054</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2286,12 +2286,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2014600</t>
+          <t>1903748</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2309,17 +2309,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2015802</t>
+          <t>1904824</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2332,7 +2332,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>204058</t>
+          <t>2000813</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2355,7 +2355,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>205341</t>
+          <t>200231</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2378,12 +2378,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>207050</t>
+          <t>2002880</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2401,17 +2401,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>211246</t>
+          <t>2003113</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2424,12 +2424,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>211601</t>
+          <t>2014328</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2447,17 +2447,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>211693</t>
+          <t>2014462</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2470,17 +2470,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>212446</t>
+          <t>2014872</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2493,17 +2493,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>214586</t>
+          <t>2014899</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2516,17 +2516,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>214858</t>
+          <t>2015481</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2539,17 +2539,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>215904</t>
+          <t>2015765</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2562,7 +2562,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>216244</t>
+          <t>202375</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2585,17 +2585,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>216957</t>
+          <t>204332</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2608,12 +2608,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>217144</t>
+          <t>205738</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>217187</t>
+          <t>206311</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2654,17 +2654,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>217439</t>
+          <t>207975</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2677,17 +2677,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>218348</t>
+          <t>210640</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2700,7 +2700,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>218483</t>
+          <t>212366</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2723,7 +2723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>218866</t>
+          <t>212618</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2746,17 +2746,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>219644</t>
+          <t>216969</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2769,17 +2769,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2202787</t>
+          <t>217255</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2792,12 +2792,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2203098</t>
+          <t>217390</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>220845</t>
+          <t>217525</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -2838,12 +2838,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>222948</t>
+          <t>217866</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2861,12 +2861,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>223086</t>
+          <t>218059</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>224410</t>
+          <t>218113</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>227338</t>
+          <t>218155</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2930,12 +2930,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>228878</t>
+          <t>218592</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2953,7 +2953,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>229187</t>
+          <t>219640</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -2976,12 +2976,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>229522</t>
+          <t>2200665</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>230548</t>
+          <t>2200839</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3022,12 +3022,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2313934</t>
+          <t>2201397</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3045,12 +3045,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>232975</t>
+          <t>2202112</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3068,17 +3068,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>233029</t>
+          <t>2202513</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -3091,12 +3091,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>233117</t>
+          <t>2202817</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3114,17 +3114,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>233411</t>
+          <t>2202904</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3137,17 +3137,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>233826</t>
+          <t>2204162</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3160,12 +3160,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>234282</t>
+          <t>2205170</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>234916</t>
+          <t>220533</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -3206,12 +3206,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>236317</t>
+          <t>2205697</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3229,17 +3229,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>236554</t>
+          <t>2205926</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -3252,12 +3252,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>237676</t>
+          <t>2206088</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3275,17 +3275,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>239050</t>
+          <t>221343</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -3298,7 +3298,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2410892</t>
+          <t>223758</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -3321,7 +3321,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>242001</t>
+          <t>224235</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -3344,12 +3344,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>245057</t>
+          <t>224329</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3367,17 +3367,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>245174</t>
+          <t>225953</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -3390,17 +3390,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>246681</t>
+          <t>228147</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -3413,12 +3413,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>246854</t>
+          <t>228275</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3436,7 +3436,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2613184</t>
+          <t>229161</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -3459,17 +3459,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2613951</t>
+          <t>229372</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3482,17 +3482,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2617982</t>
+          <t>2300628</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3505,17 +3505,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2802342</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -3528,17 +3528,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2900402</t>
+          <t>2313267</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -3551,17 +3551,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>300452</t>
+          <t>2313953</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -3574,17 +3574,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>301065</t>
+          <t>2314073</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -3597,12 +3597,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>301530</t>
+          <t>232256</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3620,17 +3620,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>302508</t>
+          <t>233449</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3643,17 +3643,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>233834</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -3666,7 +3666,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3303648</t>
+          <t>234398</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3689,17 +3689,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3304180</t>
+          <t>235207</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3712,12 +3712,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3308361</t>
+          <t>235511</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3735,17 +3735,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3308601</t>
+          <t>240973</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -3758,17 +3758,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3309536</t>
+          <t>241038</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -3781,17 +3781,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3600999</t>
+          <t>242928</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -3804,7 +3804,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3601415</t>
+          <t>245354</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3827,7 +3827,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3601577</t>
+          <t>2602352</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3850,12 +3850,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3601969</t>
+          <t>2602467</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3602598</t>
+          <t>2602563</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -3896,17 +3896,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3603839</t>
+          <t>2613306</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3919,7 +3919,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3605001</t>
+          <t>2617802</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -3942,12 +3942,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3605063</t>
+          <t>2800768</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3965,12 +3965,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3605405</t>
+          <t>2801234</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3988,17 +3988,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3605869</t>
+          <t>2801890</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4011,17 +4011,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3701679</t>
+          <t>2801923</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -4034,17 +4034,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3704130</t>
+          <t>300021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -4057,12 +4057,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4000029</t>
+          <t>301074</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4080,12 +4080,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4000840</t>
+          <t>301076</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4103,17 +4103,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>400811</t>
+          <t>301083</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4126,17 +4126,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>400816</t>
+          <t>301153</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -4149,17 +4149,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4104537</t>
+          <t>301306</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4172,7 +4172,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4300679</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4195,7 +4195,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4301141</t>
+          <t>302724</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4218,17 +4218,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4302511</t>
+          <t>303440</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -4241,17 +4241,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4302657</t>
+          <t>305541</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -4264,12 +4264,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4303773</t>
+          <t>305706</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4287,17 +4287,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4305445</t>
+          <t>305944</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -4310,17 +4310,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4305515</t>
+          <t>3101237</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -4333,7 +4333,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4305534</t>
+          <t>3101385</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -4356,12 +4356,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4305994</t>
+          <t>3102733</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4379,12 +4379,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4306494</t>
+          <t>3104804</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4402,17 +4402,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4306959</t>
+          <t>3300690</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -4425,17 +4425,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4307223</t>
+          <t>3302461</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -4448,17 +4448,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4307429</t>
+          <t>3302562</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -4471,7 +4471,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4308800</t>
+          <t>3302580</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -4494,17 +4494,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4309780</t>
+          <t>3305861</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4517,12 +4517,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4310846</t>
+          <t>3306575</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4313017</t>
+          <t>3306857</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4563,12 +4563,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4313257</t>
+          <t>3308087</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4586,17 +4586,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4314016</t>
+          <t>3600511</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -4609,7 +4609,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4317093</t>
+          <t>3600581</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -4632,7 +4632,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4317098</t>
+          <t>3600777</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -4655,17 +4655,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4318405</t>
+          <t>3600905</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4678,7 +4678,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4319173</t>
+          <t>3601688</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4701,7 +4701,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5000378</t>
+          <t>3604774</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -4724,12 +4724,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>504778</t>
+          <t>3604834</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4747,17 +4747,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5200128</t>
+          <t>3604947</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4770,12 +4770,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5200459</t>
+          <t>3605337</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4793,7 +4793,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5200689</t>
+          <t>3605378</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -4816,7 +4816,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5202555</t>
+          <t>3701714</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -4839,7 +4839,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5203525</t>
+          <t>3704621</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -4862,17 +4862,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5205616</t>
+          <t>4000056</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4885,7 +4885,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5205637</t>
+          <t>400817</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -4908,17 +4908,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5206600</t>
+          <t>4101188</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -4931,7 +4931,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5207448</t>
+          <t>4101229</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -4954,7 +4954,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5208033</t>
+          <t>4200457</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4977,17 +4977,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5208231</t>
+          <t>4301476</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -5000,12 +5000,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5209188</t>
+          <t>4302408</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5023,12 +5023,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5212868</t>
+          <t>4302850</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5046,17 +5046,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5213239</t>
+          <t>4303349</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -5069,17 +5069,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5213618</t>
+          <t>4303382</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -5092,12 +5092,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5214964</t>
+          <t>4304564</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5115,17 +5115,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5217018</t>
+          <t>4304939</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -5138,17 +5138,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5217130</t>
+          <t>4305594</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -5161,17 +5161,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5218531</t>
+          <t>4307324</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -5184,17 +5184,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5219495</t>
+          <t>4307797</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -5207,7 +5207,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5500572</t>
+          <t>4308082</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5230,12 +5230,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5501885</t>
+          <t>4308403</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5253,12 +5253,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5502079</t>
+          <t>4308933</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5276,17 +5276,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5609346</t>
+          <t>4311567</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -5299,17 +5299,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5900045</t>
+          <t>4312184</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -5322,7 +5322,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>600644</t>
+          <t>4312576</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -5345,17 +5345,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>601005</t>
+          <t>4313041</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -5368,12 +5368,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>601106</t>
+          <t>4313732</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5391,17 +5391,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>601639</t>
+          <t>4313876</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -5414,17 +5414,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>602081</t>
+          <t>4313988</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -5437,12 +5437,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>602720</t>
+          <t>4316564</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5460,12 +5460,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>604092</t>
+          <t>4316803</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>605933</t>
+          <t>4317331</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5506,17 +5506,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>606560</t>
+          <t>4317745</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -5529,7 +5529,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>607454</t>
+          <t>4319002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -5552,7 +5552,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>608191</t>
+          <t>4400128</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -5575,7 +5575,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6100883</t>
+          <t>4801559</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -5598,7 +5598,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>610397</t>
+          <t>5200438</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5621,17 +5621,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>610886</t>
+          <t>5201159</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -5644,12 +5644,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>611830</t>
+          <t>5202329</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>612125</t>
+          <t>5202588</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -5690,7 +5690,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>612142</t>
+          <t>5202770</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -5713,17 +5713,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>612523</t>
+          <t>5203015</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5736,17 +5736,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>612589</t>
+          <t>5203370</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -5759,17 +5759,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>616698</t>
+          <t>5204166</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -5782,7 +5782,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>617100</t>
+          <t>5204542</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -5805,7 +5805,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>617182</t>
+          <t>5204932</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5828,17 +5828,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>617294</t>
+          <t>5205131</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -5851,17 +5851,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>619312</t>
+          <t>5205626</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -5874,12 +5874,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>6703886</t>
+          <t>5206066</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5897,17 +5897,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>6900157</t>
+          <t>5206339</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -5920,17 +5920,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>7000003</t>
+          <t>5207112</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -5943,12 +5943,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>7000715</t>
+          <t>5207290</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5966,7 +5966,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>7000827</t>
+          <t>5207321</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -5989,17 +5989,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>701152</t>
+          <t>5208705</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -6012,7 +6012,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>7100059</t>
+          <t>5209046</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6035,17 +6035,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>7205670</t>
+          <t>5209630</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -6058,12 +6058,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7206216</t>
+          <t>5210715</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6081,17 +6081,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>7206855</t>
+          <t>5210786</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -6104,17 +6104,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>7500731</t>
+          <t>5212894</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -6127,12 +6127,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>9200421</t>
+          <t>5214063</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6150,17 +6150,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>9201165</t>
+          <t>5214093</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -6173,17 +6173,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>9202543</t>
+          <t>5216836</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -6196,17 +6196,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>9202579</t>
+          <t>5218093</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -6219,17 +6219,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>9204964</t>
+          <t>5218292</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -6242,12 +6242,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>9205088</t>
+          <t>5218460</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6265,17 +6265,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>9206197</t>
+          <t>5219498</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6288,17 +6288,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>9207232</t>
+          <t>5219714</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -6311,12 +6311,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>9400278</t>
+          <t>5502392</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6334,7 +6334,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>9400422</t>
+          <t>5502431</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6357,17 +6357,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9400913</t>
+          <t>5503103</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6380,17 +6380,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>9500548</t>
+          <t>5503188</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -6403,17 +6403,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>9501173</t>
+          <t>601830</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -6426,17 +6426,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>9501594</t>
+          <t>603631</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6449,12 +6449,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>9502482</t>
+          <t>604315</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6472,17 +6472,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>9502937</t>
+          <t>604932</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6495,17 +6495,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>9503137</t>
+          <t>605396</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -6518,23 +6518,1380 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>9503361</t>
+          <t>606146</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>606423</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>606767</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>606874</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>607122</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>608178</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>608470</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>609823</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>610586</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>611338</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>612499</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>612836</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>614359</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>614886</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>615488</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>616050</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>616443</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>616697</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>616935</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>617065</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>617107</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>618068</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>618463</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>6600153</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>6600641</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>6600774</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>6900032</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>7000253</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>7000596</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>7000631</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>7201644</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>7201657</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>7201871</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>7202027</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>7202101</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>7202102</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>7205708</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>7500356</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>7501478</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>7504432</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>7506209</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E266" t="n">
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>8500013</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>9200159</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>9200836</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>9201001</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>9201048</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>9201614</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>9201623</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>9202482</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>9202557</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>9202974</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>9203212</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>9204457</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>9204729</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>9204771</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>9205166</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>9400047</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>9400592</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>9500705</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>9503113</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E325" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Grade&Con_Compara.xlsx
+++ b/Grade&Con_Compara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E325"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10001619</t>
+          <t>10000369</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -469,17 +469,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10001806</t>
+          <t>10001926</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10002252</t>
+          <t>10005044</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10007229</t>
+          <t>10005079</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -538,12 +538,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10007754</t>
+          <t>10007939</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -561,17 +561,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10009188</t>
+          <t>10008055</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -584,17 +584,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10009651</t>
+          <t>1000981</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -607,12 +607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10011043</t>
+          <t>10011097</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10011461</t>
+          <t>10011340</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -653,12 +653,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10013059</t>
+          <t>10013245</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10013349</t>
+          <t>10013289</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -699,12 +699,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10013764</t>
+          <t>10013484</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -722,17 +722,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10013956</t>
+          <t>10013756</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -745,7 +745,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10015023</t>
+          <t>10014023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -768,17 +768,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10016760</t>
+          <t>10014463</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -791,12 +791,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10017752</t>
+          <t>10014499</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10018833</t>
+          <t>10016569</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,17 +837,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1003192</t>
+          <t>101083</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -860,7 +860,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>101074</t>
+          <t>101800</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>101646</t>
+          <t>102278</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -906,17 +906,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>103587</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -929,17 +929,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>104245</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -952,7 +952,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>104823</t>
+          <t>104341</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>105036</t>
+          <t>104877</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -998,7 +998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>106151</t>
+          <t>105210</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1021,17 +1021,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>108072</t>
+          <t>105263</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1044,17 +1044,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>108308</t>
+          <t>106363</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1067,7 +1067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>108312</t>
+          <t>106948</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1090,12 +1090,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>108361</t>
+          <t>108142</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>108607</t>
+          <t>108337</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>108625</t>
+          <t>108624</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>109073</t>
+          <t>109449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1182,17 +1182,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>110240</t>
+          <t>110159</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1205,17 +1205,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>110976</t>
+          <t>110325</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1228,7 +1228,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>111861</t>
+          <t>110494</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1251,12 +1251,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>112362</t>
+          <t>110657</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1274,12 +1274,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>113408</t>
+          <t>110779</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>114030</t>
+          <t>111853</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1303173</t>
+          <t>112273</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1343,12 +1343,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1303833</t>
+          <t>113962</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1305866</t>
+          <t>1200073</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1389,12 +1389,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1307898</t>
+          <t>1302803</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1412,7 +1412,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1308834</t>
+          <t>1306438</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1435,17 +1435,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1400131</t>
+          <t>1306508</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1458,17 +1458,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1400928</t>
+          <t>1306878</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1481,12 +1481,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1401086</t>
+          <t>1309330</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1401197</t>
+          <t>1313945</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1527,12 +1527,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1601450</t>
+          <t>1400498</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1550,17 +1550,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1602160</t>
+          <t>1400684</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1573,7 +1573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1602494</t>
+          <t>1400905</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1603162</t>
+          <t>1400996</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1604572</t>
+          <t>1500708</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1642,17 +1642,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1604620</t>
+          <t>1600757</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1665,12 +1665,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1605583</t>
+          <t>1601472</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1688,17 +1688,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1605744</t>
+          <t>1602621</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1711,12 +1711,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1605803</t>
+          <t>1602768</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1607131</t>
+          <t>1602977</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1608523</t>
+          <t>1604142</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1780,7 +1780,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1608554</t>
+          <t>1604436</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1803,12 +1803,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1609216</t>
+          <t>1605672</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1826,17 +1826,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1615341</t>
+          <t>1608782</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1849,12 +1849,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1616828</t>
+          <t>1609303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1872,17 +1872,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1617868</t>
+          <t>1610115</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1895,12 +1895,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1618142</t>
+          <t>1610207</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1618327</t>
+          <t>1610469</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1941,17 +1941,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1619026</t>
+          <t>1611325</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1964,17 +1964,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1619154</t>
+          <t>1611757</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1987,12 +1987,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1619509</t>
+          <t>1612086</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1620561</t>
+          <t>1613494</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2033,12 +2033,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1620621</t>
+          <t>1613564</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2056,17 +2056,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1623442</t>
+          <t>1615021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2079,12 +2079,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1626785</t>
+          <t>1616364</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2102,17 +2102,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1627634</t>
+          <t>1617920</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2125,17 +2125,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1627856</t>
+          <t>1618341</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2148,17 +2148,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1628389</t>
+          <t>1618369</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2171,17 +2171,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1700254</t>
+          <t>1619592</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2194,17 +2194,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1702457</t>
+          <t>1620527</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2217,12 +2217,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1901168</t>
+          <t>1620967</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2240,17 +2240,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1901987</t>
+          <t>1621535</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2263,12 +2263,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1902054</t>
+          <t>1621663</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2286,12 +2286,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1903748</t>
+          <t>1621945</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2309,12 +2309,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1904824</t>
+          <t>1622982</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2332,12 +2332,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2000813</t>
+          <t>1627060</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2355,17 +2355,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>200231</t>
+          <t>1627167</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2378,7 +2378,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2002880</t>
+          <t>1627487</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2401,7 +2401,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2003113</t>
+          <t>1627864</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2424,17 +2424,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2014328</t>
+          <t>1629550</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -2447,17 +2447,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2014462</t>
+          <t>1630079</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2470,12 +2470,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2014872</t>
+          <t>1630205</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2014899</t>
+          <t>1630231</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2516,17 +2516,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2015481</t>
+          <t>1701027</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2539,17 +2539,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2015765</t>
+          <t>1702270</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2562,17 +2562,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>202375</t>
+          <t>1702507</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2585,17 +2585,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>204332</t>
+          <t>1800033</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2608,17 +2608,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>205738</t>
+          <t>1901324</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2631,7 +2631,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>206311</t>
+          <t>1901462</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2654,17 +2654,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>207975</t>
+          <t>1901633</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2677,12 +2677,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>210640</t>
+          <t>1901678</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2700,12 +2700,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>212366</t>
+          <t>1901859</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2723,12 +2723,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>212618</t>
+          <t>1901964</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>216969</t>
+          <t>1902294</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2769,17 +2769,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>217255</t>
+          <t>1902461</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2792,12 +2792,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>217390</t>
+          <t>2000562</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>2001475</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2838,17 +2838,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>217866</t>
+          <t>200160</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2861,17 +2861,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>218059</t>
+          <t>2001999</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2884,12 +2884,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>218113</t>
+          <t>2002535</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>218155</t>
+          <t>2003134</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2930,17 +2930,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>218592</t>
+          <t>200353</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2953,17 +2953,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>219640</t>
+          <t>2003568</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -2976,17 +2976,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2200665</t>
+          <t>2013954</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -2999,17 +2999,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2200839</t>
+          <t>2014272</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3022,12 +3022,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2201397</t>
+          <t>2014690</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3045,12 +3045,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2202112</t>
+          <t>2014953</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3068,12 +3068,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2202513</t>
+          <t>2015289</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3091,17 +3091,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2202817</t>
+          <t>2015580</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -3114,7 +3114,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2202904</t>
+          <t>2015918</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3137,17 +3137,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2204162</t>
+          <t>202796</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3160,17 +3160,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2205170</t>
+          <t>202941</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3183,7 +3183,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>220533</t>
+          <t>202984</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -3206,17 +3206,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2205697</t>
+          <t>204873</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -3229,17 +3229,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2205926</t>
+          <t>206452</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -3252,7 +3252,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2206088</t>
+          <t>208216</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -3275,7 +3275,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>221343</t>
+          <t>208756</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -3298,12 +3298,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>223758</t>
+          <t>210623</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>224235</t>
+          <t>210667</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3344,17 +3344,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>224329</t>
+          <t>211029</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -3367,7 +3367,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>225953</t>
+          <t>211038</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3390,17 +3390,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>228147</t>
+          <t>211407</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -3413,12 +3413,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>228275</t>
+          <t>213168</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3436,7 +3436,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>229161</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -3459,7 +3459,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>229372</t>
+          <t>216941</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3482,12 +3482,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2300628</t>
+          <t>219025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3505,12 +3505,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>2200580</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3528,12 +3528,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2313267</t>
+          <t>2200734</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3551,17 +3551,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2313953</t>
+          <t>2200979</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -3574,7 +3574,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2314073</t>
+          <t>2202492</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -3597,12 +3597,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>232256</t>
+          <t>2203185</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3620,17 +3620,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>233449</t>
+          <t>2204916</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3643,7 +3643,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>233834</t>
+          <t>2205370</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -3666,17 +3666,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>234398</t>
+          <t>2205739</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -3689,7 +3689,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>235207</t>
+          <t>2206308</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3712,7 +3712,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>235511</t>
+          <t>222199</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3735,7 +3735,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>240973</t>
+          <t>222559</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -3758,12 +3758,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>241038</t>
+          <t>223140</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>223641</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3804,12 +3804,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>245354</t>
+          <t>223983</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3827,17 +3827,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2602352</t>
+          <t>224277</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3850,12 +3850,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2602467</t>
+          <t>225416</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2602563</t>
+          <t>227076</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -3896,17 +3896,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2613306</t>
+          <t>228611</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3919,12 +3919,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2617802</t>
+          <t>228818</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3942,17 +3942,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2800768</t>
+          <t>229708</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -3965,12 +3965,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2801234</t>
+          <t>229795</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3988,7 +3988,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2801890</t>
+          <t>2300016</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4011,17 +4011,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2801923</t>
+          <t>2300396</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -4034,12 +4034,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>300021</t>
+          <t>2313681</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4057,17 +4057,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>301074</t>
+          <t>233171</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4080,12 +4080,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>301076</t>
+          <t>234400</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4103,17 +4103,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>301083</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4126,12 +4126,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>301153</t>
+          <t>235005</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>301306</t>
+          <t>238896</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4172,17 +4172,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>302681</t>
+          <t>239328</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -4195,12 +4195,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>302724</t>
+          <t>239367</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4218,7 +4218,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>303440</t>
+          <t>2400556</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -4241,12 +4241,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>305541</t>
+          <t>2401184</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4264,17 +4264,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>305706</t>
+          <t>2401238</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -4287,17 +4287,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>305944</t>
+          <t>241750</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -4310,7 +4310,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3101237</t>
+          <t>243058</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4333,7 +4333,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3101385</t>
+          <t>243337</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4356,17 +4356,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3102733</t>
+          <t>245353</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -4379,17 +4379,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3104804</t>
+          <t>247352</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -4402,7 +4402,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3300690</t>
+          <t>2600755</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4425,12 +4425,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3302461</t>
+          <t>2601165</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4448,17 +4448,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3302562</t>
+          <t>2617229</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -4471,12 +4471,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3302580</t>
+          <t>2617316</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4494,17 +4494,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3305861</t>
+          <t>2617860</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4517,17 +4517,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3306575</t>
+          <t>2800668</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4540,7 +4540,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3306857</t>
+          <t>2801453</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4563,17 +4563,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3308087</t>
+          <t>2802060</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4586,12 +4586,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3600511</t>
+          <t>2804462</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4609,12 +4609,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3600581</t>
+          <t>2900040</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3600777</t>
+          <t>300530</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -4655,17 +4655,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3600905</t>
+          <t>301017</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4678,7 +4678,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3601688</t>
+          <t>301551</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4701,17 +4701,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3604774</t>
+          <t>301612</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -4724,7 +4724,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3604834</t>
+          <t>302670</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4747,12 +4747,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3604947</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3605337</t>
+          <t>303714</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3605378</t>
+          <t>305335</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3701714</t>
+          <t>305824</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4839,12 +4839,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3704621</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4862,17 +4862,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4000056</t>
+          <t>306021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4885,17 +4885,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>400817</t>
+          <t>3101330</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -4908,17 +4908,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4101188</t>
+          <t>3101659</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -4931,7 +4931,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4101229</t>
+          <t>3102216</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>4200457</t>
+          <t>3103385</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4977,17 +4977,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4301476</t>
+          <t>3105463</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -5000,12 +5000,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4302408</t>
+          <t>3300568</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5023,17 +5023,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4302850</t>
+          <t>3300871</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -5046,17 +5046,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4303349</t>
+          <t>3301009</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -5069,17 +5069,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4303382</t>
+          <t>3301192</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -5092,7 +5092,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>4304564</t>
+          <t>3302463</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -5115,7 +5115,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4304939</t>
+          <t>3302590</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -5138,7 +5138,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4305594</t>
+          <t>3303822</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -5161,17 +5161,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4307324</t>
+          <t>3305633</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -5184,17 +5184,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4307797</t>
+          <t>3306741</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -5207,17 +5207,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4308082</t>
+          <t>3307245</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -5230,7 +5230,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4308403</t>
+          <t>3307642</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5253,17 +5253,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4308933</t>
+          <t>3307902</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -5276,17 +5276,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4311567</t>
+          <t>3309378</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -5299,12 +5299,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>4312184</t>
+          <t>3601891</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5322,12 +5322,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4312576</t>
+          <t>3602686</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5345,7 +5345,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4313041</t>
+          <t>3603525</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -5368,12 +5368,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4313732</t>
+          <t>3603898</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5391,7 +5391,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4313876</t>
+          <t>3604696</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5414,12 +5414,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4313988</t>
+          <t>3604981</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5437,17 +5437,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4316564</t>
+          <t>3703008</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -5460,7 +5460,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4316803</t>
+          <t>4101692</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4317331</t>
+          <t>4104322</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5506,17 +5506,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4317745</t>
+          <t>4201292</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -5529,7 +5529,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4319002</t>
+          <t>4300592</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -5552,7 +5552,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4400128</t>
+          <t>4301672</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -5575,7 +5575,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4801559</t>
+          <t>4301895</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5598,12 +5598,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5200438</t>
+          <t>4303530</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5621,12 +5621,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5201159</t>
+          <t>4304405</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5644,7 +5644,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5202329</t>
+          <t>4304411</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -5667,7 +5667,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5202588</t>
+          <t>4304889</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -5690,12 +5690,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5202770</t>
+          <t>4305313</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5713,7 +5713,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5203015</t>
+          <t>4306135</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5736,12 +5736,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5203370</t>
+          <t>4306307</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5759,7 +5759,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5204166</t>
+          <t>4307334</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5782,7 +5782,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5204542</t>
+          <t>4307485</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -5805,7 +5805,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5204932</t>
+          <t>4308107</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5828,17 +5828,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5205131</t>
+          <t>4308346</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -5851,17 +5851,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5205626</t>
+          <t>4308470</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -5874,12 +5874,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5206066</t>
+          <t>4308632</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5897,12 +5897,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5206339</t>
+          <t>4308707</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5920,7 +5920,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5207112</t>
+          <t>4309275</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -5943,17 +5943,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5207290</t>
+          <t>4309578</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -5966,12 +5966,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5207321</t>
+          <t>4310693</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5989,17 +5989,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5208705</t>
+          <t>4311555</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -6012,17 +6012,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5209046</t>
+          <t>4312808</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -6035,12 +6035,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5209630</t>
+          <t>4313868</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6058,12 +6058,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5210715</t>
+          <t>4314146</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6081,12 +6081,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5210786</t>
+          <t>4314148</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6104,17 +6104,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5212894</t>
+          <t>4314999</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -6127,17 +6127,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5214063</t>
+          <t>4315756</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -6150,7 +6150,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5214093</t>
+          <t>4315791</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6173,17 +6173,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5216836</t>
+          <t>4315933</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -6196,17 +6196,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5218093</t>
+          <t>4319197</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -6219,7 +6219,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5218292</t>
+          <t>4319246</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -6242,7 +6242,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5218460</t>
+          <t>4909261</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6265,17 +6265,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5219498</t>
+          <t>500350</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6288,7 +6288,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5219714</t>
+          <t>500415</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -6311,17 +6311,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5502392</t>
+          <t>504605</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6334,17 +6334,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5502431</t>
+          <t>5200837</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -6357,17 +6357,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5503103</t>
+          <t>5200967</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6380,17 +6380,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5503188</t>
+          <t>5201017</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -6403,17 +6403,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>601830</t>
+          <t>5201510</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -6426,17 +6426,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>603631</t>
+          <t>5202151</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6449,12 +6449,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>604315</t>
+          <t>5202990</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6472,17 +6472,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>604932</t>
+          <t>5203587</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6495,17 +6495,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>605396</t>
+          <t>5203695</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -6518,17 +6518,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>606146</t>
+          <t>5206906</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -6541,7 +6541,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>606423</t>
+          <t>5207601</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6564,7 +6564,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>606767</t>
+          <t>5208043</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6587,17 +6587,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>606874</t>
+          <t>5208953</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -6610,7 +6610,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>607122</t>
+          <t>5209144</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -6633,17 +6633,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>608178</t>
+          <t>5209149</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -6656,7 +6656,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>608470</t>
+          <t>5209309</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6679,17 +6679,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>609823</t>
+          <t>5209566</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -6702,12 +6702,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>610586</t>
+          <t>5210253</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6725,12 +6725,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>611338</t>
+          <t>5210726</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6748,17 +6748,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>612499</t>
+          <t>5211174</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -6771,7 +6771,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>612836</t>
+          <t>5212495</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6794,12 +6794,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>614359</t>
+          <t>5213076</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6817,7 +6817,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>614886</t>
+          <t>5213659</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -6840,7 +6840,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>615488</t>
+          <t>5214897</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6863,7 +6863,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>616050</t>
+          <t>5215722</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6886,17 +6886,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>616443</t>
+          <t>5215828</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6909,12 +6909,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>616697</t>
+          <t>5216872</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6932,17 +6932,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>616935</t>
+          <t>5217815</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -6955,7 +6955,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>617065</t>
+          <t>5217887</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6978,12 +6978,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>617107</t>
+          <t>5217957</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -7001,7 +7001,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>618068</t>
+          <t>5218839</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>618463</t>
+          <t>5219719</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -7047,7 +7047,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>6600153</t>
+          <t>5500522</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -7070,12 +7070,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6600641</t>
+          <t>5500705</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7093,17 +7093,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>6600774</t>
+          <t>5501091</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -7116,12 +7116,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>6900032</t>
+          <t>5501207</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7139,12 +7139,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>7000253</t>
+          <t>5501880</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7162,17 +7162,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>7000596</t>
+          <t>5501904</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -7185,12 +7185,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>7000631</t>
+          <t>5502557</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7208,12 +7208,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>7201644</t>
+          <t>5502563</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7231,17 +7231,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>7201657</t>
+          <t>5502572</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -7254,12 +7254,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>7201871</t>
+          <t>5503227</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7277,12 +7277,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7202027</t>
+          <t>600157</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7300,17 +7300,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>7202101</t>
+          <t>600566</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -7323,17 +7323,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>7202102</t>
+          <t>600747</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -7346,17 +7346,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>7205708</t>
+          <t>600852</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -7369,12 +7369,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>7500356</t>
+          <t>600895</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7392,7 +7392,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>7501478</t>
+          <t>600904</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7415,7 +7415,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>7504432</t>
+          <t>601364</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7438,17 +7438,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>7506209</t>
+          <t>601683</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -7461,17 +7461,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>8500013</t>
+          <t>601712</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -7484,12 +7484,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>9200159</t>
+          <t>601832</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7507,17 +7507,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>9200836</t>
+          <t>602440</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -7530,17 +7530,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>9201001</t>
+          <t>602713</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -7553,17 +7553,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>9201048</t>
+          <t>603122</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -7576,7 +7576,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>9201614</t>
+          <t>603463</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7599,7 +7599,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>9201623</t>
+          <t>603532</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7622,7 +7622,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>9202482</t>
+          <t>603669</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7645,12 +7645,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>9202557</t>
+          <t>603863</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>9202974</t>
+          <t>604294</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7691,17 +7691,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>9203212</t>
+          <t>605168</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -7714,7 +7714,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>9204457</t>
+          <t>605184</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -7737,12 +7737,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>9204729</t>
+          <t>605489</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C-</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>9204771</t>
+          <t>605578</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7783,17 +7783,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>9205166</t>
+          <t>605925</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -7806,17 +7806,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>9400047</t>
+          <t>606696</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -7829,7 +7829,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>9400592</t>
+          <t>609361</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7852,12 +7852,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>9500705</t>
+          <t>609546</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7875,23 +7875,1495 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>9503113</t>
+          <t>609695</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>6100587</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>610112</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>6101989</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>611836</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>611850</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>612292</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>616993</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>617636</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>618114</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>618265</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="D325" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E325" t="n">
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>618496</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>6600131</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>6600812</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>6700550</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>6702173</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>6900230</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>7000032</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>700720</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>700739</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>701068</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>701476</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>7100136</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>7200023</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>7202657</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>7401586</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>7500430</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>7503188</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>7504506</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>7505250</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>7505694</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>7700536</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>8500006</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>9200229</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>9200478</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>9200732</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>9201001</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>9201402</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>9201637</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>9202423</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>9202503</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>9202752</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>9202952</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>9203568</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>9203578</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E369" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>9204105</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>9204905</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E371" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>9204947</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>9205306</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E373" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>9205795</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E374" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>9206794</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>9206849</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>9207615</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>9208409</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>9208912</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>9208940</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>9208987</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>AV</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E381" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>9208989</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>9209501</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E383" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>9400687</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E384" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>9500962</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E385" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>9501476</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E386" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>9501595</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E387" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>9502400</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>9502631</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E389" t="n">
         <v>1</v>
       </c>
     </row>
